--- a/Hoadon/HDVao/11/3502386218_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/11/3502386218_HDDienTuDaCapMa.xlsx
@@ -3684,32 +3684,32 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>C25THB</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>37083</t>
+          <t>31991</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>0302263527-001</t>
+          <t>0302263527</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Số 28 Phan Bội Châu, Phường Cửa Nam, TP Hà Nội, Việt Nam</t>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -3765,32 +3765,32 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C25TDA</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>0302263527-004</t>
+          <t>0302263527</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>C25TDA</t>
+          <t>C25THB</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>0302263527-004</t>
+          <t>0302263527-001</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+          <t>Số 28 Phan Bội Châu, Phường Cửa Nam, TP Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -3927,32 +3927,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C25TAA</t>
+          <t>C25TDA</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>0305412142</t>
+          <t>0302263527-004</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIẾT BỊ VĂN PHÒNG NHẬT TIẾN THANH</t>
+          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>176 Lê Hồng Phong, Phường Chợ Quán, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -3966,17 +3966,15 @@
         </is>
       </c>
       <c r="K51" s="13" t="n">
-        <v>3176900.0</v>
+        <v>4032407.0</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>254152.0</v>
-      </c>
-      <c r="M51" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>322593.0</v>
+      </c>
+      <c r="M51" s="13"/>
       <c r="N51" s="13"/>
       <c r="O51" s="13" t="n">
-        <v>3431052.0</v>
+        <v>4355000.0</v>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
@@ -4010,32 +4008,32 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>C25TPL</t>
+          <t>C25TDA</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>0309414020</t>
+          <t>0302263527-004</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -4049,17 +4047,15 @@
         </is>
       </c>
       <c r="K52" s="13" t="n">
-        <v>2.48909091E8</v>
+        <v>4032407.0</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>2.4890909E7</v>
-      </c>
-      <c r="M52" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>322593.0</v>
+      </c>
+      <c r="M52" s="13"/>
       <c r="N52" s="13"/>
       <c r="O52" s="13" t="n">
-        <v>2.738E8</v>
+        <v>4355000.0</v>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
@@ -4093,12 +4089,12 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C25TNB</t>
+          <t>C25TAA</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -4108,17 +4104,17 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>0318332896</t>
+          <t>0305412142</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NƯỚC TÂN BÌNH</t>
+          <t>CÔNG TY TNHH THIẾT BỊ VĂN PHÒNG NHẬT TIẾN THANH</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>20 Cộng Hòa, Phường Bảy Hiền, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>176 Lê Hồng Phong, Phường Chợ Quán, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -4132,34 +4128,200 @@
         </is>
       </c>
       <c r="K53" s="13" t="n">
-        <v>311111.0</v>
+        <v>3176900.0</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>24889.0</v>
+        <v>254152.0</v>
       </c>
       <c r="M53" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N53" s="13"/>
       <c r="O53" s="13" t="n">
+        <v>3431052.0</v>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C25TPL</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>0309414020</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>2.48909091E8</v>
+      </c>
+      <c r="L54" s="13" t="n">
+        <v>2.4890909E7</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13" t="n">
+        <v>2.738E8</v>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C25TNB</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>0318332896</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC TÂN BÌNH</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>20 Cộng Hòa, Phường Bảy Hiền, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="n">
+        <v>311111.0</v>
+      </c>
+      <c r="L55" s="13" t="n">
+        <v>24889.0</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13" t="n">
         <v>336000.0</v>
       </c>
-      <c r="P53" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q53" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S53" s="6" t="inlineStr">
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/11/3502386218_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/11/3502386218_HDDienTuDaCapMa.xlsx
@@ -325,32 +325,32 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TVC</t>
+          <t>C25TMS</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>453934</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0101871229</t>
+          <t>0101243150</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN VCCORP</t>
+          <t>Công ty cổ phần MISA</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Số 01, Phố Nguyễn Huy Tưởng, Phường Thanh Xuân, TP.Hà Nội</t>
+          <t>Tầng 9 Tòa nhà Technosoft, Phố Duy Tân, Phường Cầu Giấy, Thành Phố Hà Nội</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -364,17 +364,17 @@
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>2.0E7</v>
+        <v>1472000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1600000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>2.16E7</v>
+        <v>1472000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,32 +408,32 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TVC</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0107581903</t>
+          <t>0101871229</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN VCCORP</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
+          <t>Số 01, Phố Nguyễn Huy Tưởng, Phường Thanh Xuân, TP.Hà Nội</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -447,17 +447,17 @@
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>3740741.0</v>
+        <v>2.0E7</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>299259.0</v>
+        <v>1600000.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>4040000.0</v>
+        <v>2.16E7</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -496,12 +496,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>54228</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>54514</t>
+          <t>54228</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>55964</t>
+          <t>54514</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -823,32 +823,32 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>55964</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0107581903</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>38652</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>39141</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>39358</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>39358</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>39549</t>
+          <t>39359</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>39549</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>39551</t>
+          <t>39550</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>39552</t>
+          <t>39551</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>39793</t>
+          <t>39552</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>39991</t>
+          <t>39793</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>39991</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>40414</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>40414</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -1941,15 +1941,17 @@
         </is>
       </c>
       <c r="K26" s="13" t="n">
-        <v>3695370.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>295630.0</v>
-      </c>
-      <c r="M26" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N26" s="13"/>
       <c r="O26" s="13" t="n">
-        <v>3991000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -1983,32 +1985,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>40618</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -2022,15 +2024,17 @@
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>3695370.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>295630.0</v>
-      </c>
-      <c r="M27" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N27" s="13"/>
       <c r="O27" s="13" t="n">
-        <v>3991000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -2064,32 +2068,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>30515</t>
+          <t>40750</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -2103,15 +2107,17 @@
         </is>
       </c>
       <c r="K28" s="13" t="n">
-        <v>3695370.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>295630.0</v>
-      </c>
-      <c r="M28" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N28" s="13"/>
       <c r="O28" s="13" t="n">
-        <v>3991000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -2145,32 +2151,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>31347</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -2184,15 +2190,17 @@
         </is>
       </c>
       <c r="K29" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M29" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N29" s="13"/>
       <c r="O29" s="13" t="n">
-        <v>4355000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -2226,32 +2234,32 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>31348</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -2265,15 +2273,17 @@
         </is>
       </c>
       <c r="K30" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M30" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N30" s="13"/>
       <c r="O30" s="13" t="n">
-        <v>4355000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -2307,32 +2317,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>41078</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -2346,15 +2356,17 @@
         </is>
       </c>
       <c r="K31" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M31" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="n">
-        <v>4355000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -2388,32 +2400,32 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>41095</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -2427,15 +2439,17 @@
         </is>
       </c>
       <c r="K32" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M32" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="n">
-        <v>4355000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -2469,32 +2483,32 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>31351</t>
+          <t>41096</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -2508,15 +2522,17 @@
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M33" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="n">
-        <v>4355000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -2550,32 +2566,32 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>41097</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -2589,15 +2605,17 @@
         </is>
       </c>
       <c r="K34" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M34" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N34" s="13"/>
       <c r="O34" s="13" t="n">
-        <v>4355000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -2631,32 +2649,32 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>41371</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -2670,15 +2688,17 @@
         </is>
       </c>
       <c r="K35" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M35" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N35" s="13"/>
       <c r="O35" s="13" t="n">
-        <v>4355000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
@@ -2712,32 +2732,32 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>31487</t>
+          <t>41372</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -2751,15 +2771,17 @@
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>3695370.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>295630.0</v>
-      </c>
-      <c r="M36" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N36" s="13"/>
       <c r="O36" s="13" t="n">
-        <v>3991000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
@@ -2798,12 +2820,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>31488</t>
+          <t>30513</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2879,12 +2901,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2960,12 +2982,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>31670</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2994,15 +3016,15 @@
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3695370.0</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>322593.0</v>
+        <v>295630.0</v>
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="13"/>
       <c r="O39" s="13" t="n">
-        <v>4355000.0</v>
+        <v>3991000.0</v>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -3041,12 +3063,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>31347</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -3122,12 +3144,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>31672</t>
+          <t>31348</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -3203,12 +3225,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>31837</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -3284,12 +3306,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>31838</t>
+          <t>31350</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -3365,12 +3387,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>31839</t>
+          <t>31351</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -3446,12 +3468,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3527,12 +3549,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3608,12 +3630,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>31842</t>
+          <t>31487</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3642,15 +3664,15 @@
         </is>
       </c>
       <c r="K47" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3695370.0</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>322593.0</v>
+        <v>295630.0</v>
       </c>
       <c r="M47" s="13"/>
       <c r="N47" s="13"/>
       <c r="O47" s="13" t="n">
-        <v>4355000.0</v>
+        <v>3991000.0</v>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
@@ -3689,12 +3711,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -3723,15 +3745,15 @@
         </is>
       </c>
       <c r="K48" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3695370.0</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>322593.0</v>
+        <v>295630.0</v>
       </c>
       <c r="M48" s="13"/>
       <c r="N48" s="13"/>
       <c r="O48" s="13" t="n">
-        <v>4355000.0</v>
+        <v>3991000.0</v>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
@@ -3770,12 +3792,12 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>31992</t>
+          <t>31489</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -3804,15 +3826,15 @@
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3695370.0</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>322593.0</v>
+        <v>295630.0</v>
       </c>
       <c r="M49" s="13"/>
       <c r="N49" s="13"/>
       <c r="O49" s="13" t="n">
-        <v>4355000.0</v>
+        <v>3991000.0</v>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
@@ -3846,32 +3868,32 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>C25THB</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>37083</t>
+          <t>31670</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>0302263527-001</t>
+          <t>0302263527</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Số 28 Phan Bội Châu, Phường Cửa Nam, TP Hà Nội, Việt Nam</t>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -3927,32 +3949,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C25TDA</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>0302263527-004</t>
+          <t>0302263527</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -4008,32 +4030,32 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>C25TDA</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>31672</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>0302263527-004</t>
+          <t>0302263527</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -4089,32 +4111,32 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C25TAA</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>0305412142</t>
+          <t>0302263527</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIẾT BỊ VĂN PHÒNG NHẬT TIẾN THANH</t>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>176 Lê Hồng Phong, Phường Chợ Quán, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -4128,17 +4150,15 @@
         </is>
       </c>
       <c r="K53" s="13" t="n">
-        <v>3176900.0</v>
+        <v>4032407.0</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>254152.0</v>
-      </c>
-      <c r="M53" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>322593.0</v>
+      </c>
+      <c r="M53" s="13"/>
       <c r="N53" s="13"/>
       <c r="O53" s="13" t="n">
-        <v>3431052.0</v>
+        <v>4355000.0</v>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
@@ -4172,32 +4192,32 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>C25TPL</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>0309414020</t>
+          <t>0302263527</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -4211,17 +4231,15 @@
         </is>
       </c>
       <c r="K54" s="13" t="n">
-        <v>2.48909091E8</v>
+        <v>4032407.0</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>2.4890909E7</v>
-      </c>
-      <c r="M54" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>322593.0</v>
+      </c>
+      <c r="M54" s="13"/>
       <c r="N54" s="13"/>
       <c r="O54" s="13" t="n">
-        <v>2.738E8</v>
+        <v>4355000.0</v>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
@@ -4255,32 +4273,32 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>C25TNB</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>31839</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>0318332896</t>
+          <t>0302263527</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NƯỚC TÂN BÌNH</t>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>20 Cộng Hòa, Phường Bảy Hiền, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -4294,34 +4312,1986 @@
         </is>
       </c>
       <c r="K55" s="13" t="n">
-        <v>311111.0</v>
+        <v>4032407.0</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>24889.0</v>
-      </c>
-      <c r="M55" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>322593.0</v>
+      </c>
+      <c r="M55" s="13"/>
       <c r="N55" s="13"/>
       <c r="O55" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>31840</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L56" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>31841</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L57" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>31842</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L58" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>31991</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>31992</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L60" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q60" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>32201</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L61" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>32202</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q62" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>32203</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S63" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>32452</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S64" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>32453</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>32454</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S66" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>32455</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L67" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q67" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L68" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>32473</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>24/11/2025</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C25TAD</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education Vietnam</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="n">
+        <v>2.3194689E7</v>
+      </c>
+      <c r="L70" s="13" t="n">
+        <v>1855575.0</v>
+      </c>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13" t="n">
+        <v>2.5050264E7</v>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>C25TAD</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH The Forum Education Vietnam</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="n">
+        <v>1325925.0</v>
+      </c>
+      <c r="L71" s="13" t="n">
+        <v>66296.0</v>
+      </c>
+      <c r="M71" s="13"/>
+      <c r="N71" s="13"/>
+      <c r="O71" s="13" t="n">
+        <v>1392221.0</v>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>C25THB</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>37083</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>0302263527-001</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Số 28 Phan Bội Châu, Phường Cửa Nam, TP Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L72" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13"/>
+      <c r="O72" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q72" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>C25TDA</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>0302263527-004</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L73" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13"/>
+      <c r="O73" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q73" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S73" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>C25TDA</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>0302263527-004</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L74" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q74" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S74" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>C25TAA</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>7087</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>0305412142</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THIẾT BỊ VĂN PHÒNG NHẬT TIẾN THANH</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>176 Lê Hồng Phong, Phường Chợ Quán, TP. Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="n">
+        <v>3176900.0</v>
+      </c>
+      <c r="L75" s="13" t="n">
+        <v>254152.0</v>
+      </c>
+      <c r="M75" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N75" s="13"/>
+      <c r="O75" s="13" t="n">
+        <v>3431052.0</v>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q75" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>C25TPL</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>0309414020</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="n">
+        <v>2.48909091E8</v>
+      </c>
+      <c r="L76" s="13" t="n">
+        <v>2.4890909E7</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N76" s="13"/>
+      <c r="O76" s="13" t="n">
+        <v>2.738E8</v>
+      </c>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q76" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S76" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>0311567151</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ VỆ SINH BÌNH PHƯƠNG</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>22/47A Tân Hóa, Phường Minh Phụng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="n">
+        <v>1.1608846E7</v>
+      </c>
+      <c r="L77" s="13" t="n">
+        <v>928708.0</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N77" s="13"/>
+      <c r="O77" s="13" t="n">
+        <v>1.2537554E7</v>
+      </c>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q77" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S77" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>C25TNB</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>0318332896</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC TÂN BÌNH</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>20 Cộng Hòa, Phường Bảy Hiền, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="n">
+        <v>311111.0</v>
+      </c>
+      <c r="L78" s="13" t="n">
+        <v>24889.0</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N78" s="13"/>
+      <c r="O78" s="13" t="n">
         <v>336000.0</v>
       </c>
-      <c r="P55" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q55" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S55" s="6" t="inlineStr">
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q78" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>73.0</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>5063</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>3502413292</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÀO TẠO HANEX</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>85 Nguyễn Thái Học, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="n">
+        <v>1275462.0</v>
+      </c>
+      <c r="L79" s="13" t="n">
+        <v>102038.0</v>
+      </c>
+      <c r="M79" s="13" t="n">
+        <v>67130.0</v>
+      </c>
+      <c r="N79" s="13"/>
+      <c r="O79" s="13" t="n">
+        <v>1377500.0</v>
+      </c>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q79" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
